--- a/artfynd/A 62340-2021 artfynd.xlsx
+++ b/artfynd/A 62340-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62340-2021 artfynd.xlsx
+++ b/artfynd/A 62340-2021 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>122057197</v>
       </c>
       <c r="B5" t="n">
-        <v>90775</v>
+        <v>90785</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 62340-2021 artfynd.xlsx
+++ b/artfynd/A 62340-2021 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>122057197</v>
       </c>
       <c r="B5" t="n">
-        <v>90785</v>
+        <v>90797</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 62340-2021 artfynd.xlsx
+++ b/artfynd/A 62340-2021 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>122057197</v>
       </c>
       <c r="B5" t="n">
-        <v>90797</v>
+        <v>90804</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 62340-2021 artfynd.xlsx
+++ b/artfynd/A 62340-2021 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>122057197</v>
       </c>
       <c r="B5" t="n">
-        <v>90804</v>
+        <v>90809</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,11 +1048,6 @@
       </c>
       <c r="E5" t="n">
         <v>1108</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 62340-2021 artfynd.xlsx
+++ b/artfynd/A 62340-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80505664</v>
+        <v>122057197</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766945.0095952193</v>
+        <v>766834</v>
       </c>
       <c r="R2" t="n">
-        <v>7156736.040609832</v>
+        <v>7156789</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88796422</v>
+        <v>88796391</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766844.2306102742</v>
+        <v>766851</v>
       </c>
       <c r="R3" t="n">
-        <v>7156794.928457572</v>
+        <v>7156858</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +847,9 @@
           <t>2020-10-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88796391</v>
+        <v>80505664</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,17 +915,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bygdeträsk, Vb</t>
+          <t>bygdeträsk, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766850.8732016524</v>
+        <v>766945</v>
       </c>
       <c r="R4" t="n">
-        <v>7156858.017728971</v>
+        <v>7156736</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,40 +978,36 @@
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122057197</v>
+        <v>88796422</v>
       </c>
       <c r="B5" t="n">
-        <v>90809</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,14 +1016,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>bygdeträsk, Vb</t>
+          <t>Bygdeträsk, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766834</v>
+        <v>766844</v>
       </c>
       <c r="R5" t="n">
-        <v>7156789</v>
+        <v>7156795</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,12 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2020-10-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2020-10-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1079,215 @@
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126320161</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bygdeträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>766931</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7156692</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126320277</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bygdeträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>766916</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7156702</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62340-2021 artfynd.xlsx
+++ b/artfynd/A 62340-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122057197</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88796391</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80505664</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88796422</t>
         </is>
       </c>
     </row>
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126320161</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,8 +1318,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126320277</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>